--- a/02_DIA_inicio_2026_analisis_assets/rbd_9600_escuela-nanihue_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9600_escuela-nanihue_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F5EF52A-06D9-4342-94AB-32F1A98DAA3B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5584C880-D01F-4A7D-B2C9-8664B54A2213}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{285558B4-A473-4A65-B89E-A16DA5DABF02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F987458E-70E4-4FF1-A195-3F9E13E25DE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{790A7987-B612-45F0-ACFB-20805DCA3494}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61823214-64A3-48B1-9AD9-0DFAFF20E309}"/>
 </file>